--- a/solute/solute.xlsx
+++ b/solute/solute.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/93c922c6a9738126/Documents/Desktop/Module Calc Project/SepCal/solute_density/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_F25DC773A252ABDACC10480E095A4B565BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FAC95CD-1770-4A57-94F8-F042CA34970A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5844B6F-4B73-4680-A93B-7E856EBFCD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="palm_oil" sheetId="1" r:id="rId1"/>
+    <sheet name="A" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -475,13 +475,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.73046875" customWidth="1"/>
+    <col min="1" max="1" width="17.77734375" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -489,7 +489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>899.37</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>10</v>
       </c>
@@ -507,7 +507,7 @@
         <v>894.553</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>20</v>
       </c>
@@ -515,7 +515,7 @@
         <v>890.1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>30</v>
       </c>
@@ -523,7 +523,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>40</v>
       </c>
@@ -531,7 +531,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>50</v>
       </c>
@@ -539,7 +539,7 @@
         <v>875.1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>60</v>
       </c>
@@ -547,7 +547,7 @@
         <v>870.2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>70</v>
       </c>
@@ -555,7 +555,7 @@
         <v>865.4</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>80</v>
       </c>
@@ -563,7 +563,7 @@
         <v>860.7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>90</v>
       </c>
@@ -571,7 +571,7 @@
         <v>856.1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>100</v>
       </c>
